--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\Project\Vamsurlike\Vamsurlike\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB68FF6C-CAE7-4216-B79D-B2AF9D277A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A7BCA8-A043-4716-8A33-10F48E848727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30216" yWindow="1728" windowWidth="28284" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30060" yWindow="1308" windowWidth="28284" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enemy" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -144,6 +144,10 @@
   </si>
   <si>
     <t>MaxHealth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MummyLord</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -194,7 +198,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -231,6 +235,12 @@
         <bgColor rgb="FFD86DCD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -261,7 +271,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -313,6 +323,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -624,7 +637,7 @@
       <c r="K3" s="2"/>
     </row>
     <row r="4" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="A4" s="4">
+      <c r="A4" s="22">
         <v>260101</v>
       </c>
       <c r="B4" s="21" t="s">
@@ -649,7 +662,7 @@
       <c r="K4" s="2"/>
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="4">
+      <c r="A5" s="22">
         <v>260102</v>
       </c>
       <c r="B5" s="7" t="s">
@@ -674,7 +687,7 @@
       <c r="K5" s="2"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="4">
+      <c r="A6" s="22">
         <v>260103</v>
       </c>
       <c r="B6" s="10" t="s">
@@ -699,7 +712,7 @@
       <c r="K6" s="6"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="4">
+      <c r="A7" s="22">
         <v>260104</v>
       </c>
       <c r="B7" s="10" t="s">
@@ -724,7 +737,7 @@
       <c r="K7" s="6"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="4">
+      <c r="A8" s="22">
         <v>260105</v>
       </c>
       <c r="B8" s="10" t="s">
@@ -749,7 +762,7 @@
       <c r="K8" s="6"/>
     </row>
     <row r="9" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="4">
+      <c r="A9" s="22">
         <v>260106</v>
       </c>
       <c r="B9" s="11" t="s">
@@ -774,7 +787,7 @@
       <c r="K9" s="6"/>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="4">
+      <c r="A10" s="22">
         <v>260107</v>
       </c>
       <c r="B10" s="11" t="s">
@@ -799,7 +812,7 @@
       <c r="K10" s="6"/>
     </row>
     <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="4">
+      <c r="A11" s="22">
         <v>260108</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -824,7 +837,7 @@
       <c r="K11" s="6"/>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="4">
+      <c r="A12" s="22">
         <v>260208</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -849,7 +862,7 @@
       <c r="K12" s="6"/>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="4">
+      <c r="A13" s="22">
         <v>260109</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -874,7 +887,7 @@
       <c r="K13" s="6"/>
     </row>
     <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="4">
+      <c r="A14" s="22">
         <v>260209</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -899,7 +912,7 @@
       <c r="K14" s="6"/>
     </row>
     <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="4">
+      <c r="A15" s="22">
         <v>260110</v>
       </c>
       <c r="B15" s="11" t="s">
@@ -924,7 +937,7 @@
       <c r="K15" s="6"/>
     </row>
     <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="4">
+      <c r="A16" s="22">
         <v>260210</v>
       </c>
       <c r="B16" s="11" t="s">
@@ -949,7 +962,7 @@
       <c r="K16" s="6"/>
     </row>
     <row r="17" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="4">
+      <c r="A17" s="22">
         <v>260111</v>
       </c>
       <c r="B17" s="7" t="s">
@@ -974,7 +987,7 @@
       <c r="K17" s="2"/>
     </row>
     <row r="18" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="4">
+      <c r="A18" s="22">
         <v>260112</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -999,7 +1012,7 @@
       <c r="K18" s="2"/>
     </row>
     <row r="19" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="4">
+      <c r="A19" s="22">
         <v>260113</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -1024,7 +1037,7 @@
       <c r="K19" s="2"/>
     </row>
     <row r="20" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="4">
+      <c r="A20" s="22">
         <v>260213</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -1049,7 +1062,7 @@
       <c r="K20" s="2"/>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="4">
+      <c r="A21" s="22">
         <v>260114</v>
       </c>
       <c r="B21" s="13" t="s">
@@ -1074,7 +1087,7 @@
       <c r="K21" s="2"/>
     </row>
     <row r="22" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="4">
+      <c r="A22" s="22">
         <v>260214</v>
       </c>
       <c r="B22" s="13" t="s">
@@ -1099,7 +1112,7 @@
       <c r="K22" s="2"/>
     </row>
     <row r="23" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="4">
+      <c r="A23" s="22">
         <v>260115</v>
       </c>
       <c r="B23" s="11" t="s">
@@ -1124,7 +1137,7 @@
       <c r="K23" s="2"/>
     </row>
     <row r="24" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="4">
+      <c r="A24" s="22">
         <v>260215</v>
       </c>
       <c r="B24" s="11" t="s">
@@ -1174,7 +1187,7 @@
       <c r="K25" s="2"/>
     </row>
     <row r="26" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="4">
+      <c r="A26" s="22">
         <v>260216</v>
       </c>
       <c r="B26" s="13" t="s">
@@ -1203,7 +1216,7 @@
         <v>260117</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C27" s="14">
         <v>250</v>
@@ -1224,7 +1237,7 @@
       <c r="K27" s="2"/>
     </row>
     <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="4">
+      <c r="A28" s="22">
         <v>260217</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -1274,7 +1287,7 @@
       <c r="K29" s="2"/>
     </row>
     <row r="30" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="4">
+      <c r="A30" s="22">
         <v>260218</v>
       </c>
       <c r="B30" s="13" t="s">
@@ -1299,7 +1312,7 @@
       <c r="K30" s="2"/>
     </row>
     <row r="31" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="4">
+      <c r="A31" s="22">
         <v>260119</v>
       </c>
       <c r="B31" s="13" t="s">
@@ -1349,7 +1362,7 @@
       <c r="K32" s="6"/>
     </row>
     <row r="33" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="4">
+      <c r="A33" s="22">
         <v>260220</v>
       </c>
       <c r="B33" s="11" t="s">

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\Project\Vamsurlike\Vamsurlike\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A7BCA8-A043-4716-8A33-10F48E848727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBAFF1CB-D6DC-4898-AD20-322B41CB27CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30060" yWindow="1308" windowWidth="28284" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28392" yWindow="636" windowWidth="28284" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enemy" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="44">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -148,6 +148,37 @@
   </si>
   <si>
     <t>MummyLord</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>위치 오프셋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>몬스터 반지름</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PositionOffset</t>
+  </si>
+  <si>
+    <t>Radius</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1,0.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flaot[]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.08,0.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.24,0.45</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -271,7 +302,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -327,6 +358,14 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -554,7 +593,7 @@
     <col min="4" max="4" width="13.6640625" style="15" customWidth="1"/>
     <col min="5" max="5" width="16.88671875" style="15" customWidth="1"/>
     <col min="6" max="6" width="15.77734375" style="15" customWidth="1"/>
-    <col min="7" max="7" width="15.33203125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" style="26" customWidth="1"/>
     <col min="8" max="9" width="15.44140625" style="3" customWidth="1"/>
     <col min="10" max="10" width="14.77734375" style="3" customWidth="1"/>
     <col min="11" max="11" width="19.21875" style="3" customWidth="1"/>
@@ -580,8 +619,12 @@
       <c r="F1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
+      <c r="G1" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
@@ -605,8 +648,12 @@
       <c r="F2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
+      <c r="G2" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="2"/>
@@ -630,8 +677,12 @@
       <c r="F3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
+      <c r="G3" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="2"/>
@@ -655,8 +706,12 @@
       <c r="F4" s="6">
         <v>1</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
+      <c r="G4" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0.7</v>
+      </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -680,8 +735,12 @@
       <c r="F5" s="6">
         <v>1</v>
       </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="9"/>
+      <c r="G5" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="6">
+        <v>1.3</v>
+      </c>
       <c r="I5" s="9"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -705,8 +764,12 @@
       <c r="F6" s="6">
         <v>1</v>
       </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="9"/>
+      <c r="G6" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="6">
+        <v>1.3</v>
+      </c>
       <c r="I6" s="9"/>
       <c r="J6" s="2"/>
       <c r="K6" s="6"/>
@@ -730,8 +793,8 @@
       <c r="F7" s="6">
         <v>2</v>
       </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="9"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="6"/>
       <c r="I7" s="9"/>
       <c r="J7" s="2"/>
       <c r="K7" s="6"/>
@@ -755,7 +818,7 @@
       <c r="F8" s="6">
         <v>1.5</v>
       </c>
-      <c r="G8" s="6"/>
+      <c r="G8" s="25"/>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
       <c r="J8" s="2"/>
@@ -780,7 +843,7 @@
       <c r="F9" s="6">
         <v>2.5</v>
       </c>
-      <c r="G9" s="6"/>
+      <c r="G9" s="25"/>
       <c r="H9" s="6"/>
       <c r="I9" s="6"/>
       <c r="J9" s="2"/>
@@ -805,7 +868,7 @@
       <c r="F10" s="6">
         <v>2.5</v>
       </c>
-      <c r="G10" s="6"/>
+      <c r="G10" s="25"/>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
       <c r="J10" s="2"/>
@@ -830,7 +893,7 @@
       <c r="F11" s="6">
         <v>2.5</v>
       </c>
-      <c r="G11" s="6"/>
+      <c r="G11" s="25"/>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
       <c r="J11" s="2"/>
@@ -855,7 +918,7 @@
       <c r="F12" s="6">
         <v>25</v>
       </c>
-      <c r="G12" s="6"/>
+      <c r="G12" s="25"/>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="2"/>
@@ -880,7 +943,7 @@
       <c r="F13" s="6">
         <v>2</v>
       </c>
-      <c r="G13" s="6"/>
+      <c r="G13" s="25"/>
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
       <c r="J13" s="2"/>
@@ -905,7 +968,7 @@
       <c r="F14" s="6">
         <v>2</v>
       </c>
-      <c r="G14" s="6"/>
+      <c r="G14" s="25"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
       <c r="J14" s="2"/>
@@ -930,7 +993,7 @@
       <c r="F15" s="6">
         <v>3</v>
       </c>
-      <c r="G15" s="6"/>
+      <c r="G15" s="25"/>
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
       <c r="J15" s="2"/>
@@ -955,7 +1018,7 @@
       <c r="F16" s="6">
         <v>3</v>
       </c>
-      <c r="G16" s="6"/>
+      <c r="G16" s="25"/>
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
       <c r="J16" s="2"/>
@@ -980,7 +1043,7 @@
       <c r="F17" s="6">
         <v>3</v>
       </c>
-      <c r="G17" s="6"/>
+      <c r="G17" s="25"/>
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
       <c r="J17" s="2"/>
@@ -1005,7 +1068,7 @@
       <c r="F18" s="6">
         <v>2</v>
       </c>
-      <c r="G18" s="6"/>
+      <c r="G18" s="25"/>
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
       <c r="J18" s="2"/>
@@ -1030,7 +1093,7 @@
       <c r="F19" s="6">
         <v>3</v>
       </c>
-      <c r="G19" s="6"/>
+      <c r="G19" s="25"/>
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
       <c r="J19" s="2"/>
@@ -1055,7 +1118,7 @@
       <c r="F20" s="6">
         <v>3</v>
       </c>
-      <c r="G20" s="6"/>
+      <c r="G20" s="25"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
       <c r="J20" s="2"/>
@@ -1080,7 +1143,7 @@
       <c r="F21" s="6">
         <v>30</v>
       </c>
-      <c r="G21" s="6"/>
+      <c r="G21" s="25"/>
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
       <c r="J21" s="2"/>
@@ -1105,7 +1168,7 @@
       <c r="F22" s="6">
         <v>30</v>
       </c>
-      <c r="G22" s="6"/>
+      <c r="G22" s="25"/>
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
       <c r="J22" s="2"/>
@@ -1130,7 +1193,7 @@
       <c r="F23" s="6">
         <v>30</v>
       </c>
-      <c r="G23" s="6"/>
+      <c r="G23" s="25"/>
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
       <c r="J23" s="2"/>
@@ -1155,7 +1218,7 @@
       <c r="F24" s="6">
         <v>30</v>
       </c>
-      <c r="G24" s="6"/>
+      <c r="G24" s="25"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
       <c r="J24" s="2"/>
@@ -1180,7 +1243,7 @@
       <c r="F25" s="6">
         <v>2</v>
       </c>
-      <c r="G25" s="6"/>
+      <c r="G25" s="25"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
@@ -1205,7 +1268,7 @@
       <c r="F26" s="6">
         <v>2</v>
       </c>
-      <c r="G26" s="6"/>
+      <c r="G26" s="25"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
@@ -1230,7 +1293,7 @@
       <c r="F27" s="6">
         <v>25</v>
       </c>
-      <c r="G27" s="6"/>
+      <c r="G27" s="25"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
@@ -1255,7 +1318,7 @@
       <c r="F28" s="6">
         <v>25</v>
       </c>
-      <c r="G28" s="6"/>
+      <c r="G28" s="25"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
@@ -1280,7 +1343,7 @@
       <c r="F29" s="6">
         <v>50</v>
       </c>
-      <c r="G29" s="6"/>
+      <c r="G29" s="25"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
@@ -1305,7 +1368,7 @@
       <c r="F30" s="6">
         <v>50</v>
       </c>
-      <c r="G30" s="6"/>
+      <c r="G30" s="25"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
@@ -1330,7 +1393,7 @@
       <c r="F31" s="6">
         <v>0</v>
       </c>
-      <c r="G31" s="6"/>
+      <c r="G31" s="25"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
@@ -1355,7 +1418,7 @@
       <c r="F32" s="6">
         <v>50</v>
       </c>
-      <c r="G32" s="6"/>
+      <c r="G32" s="25"/>
       <c r="H32" s="6"/>
       <c r="I32" s="6"/>
       <c r="J32" s="2"/>
@@ -1380,7 +1443,7 @@
       <c r="F33" s="6">
         <v>50</v>
       </c>
-      <c r="G33" s="6"/>
+      <c r="G33" s="25"/>
       <c r="H33" s="6"/>
       <c r="I33" s="6"/>
       <c r="J33" s="2"/>
@@ -1393,7 +1456,7 @@
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
-      <c r="G34" s="2"/>
+      <c r="G34" s="23"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
@@ -1406,7 +1469,7 @@
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
-      <c r="G35" s="2"/>
+      <c r="G35" s="23"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
